--- a/resources/templates/standard/F2100-06.xlsx
+++ b/resources/templates/standard/F2100-06.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>공정면허 실기 평가서</t>
   </si>
@@ -657,12 +660,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -701,15 +706,15 @@
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
       <c r="AP1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -816,7 +821,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -842,14 +847,14 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
@@ -872,7 +877,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -886,14 +891,14 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="7"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
@@ -902,14 +907,14 @@
       <c r="W5" s="5"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE5" s="5"/>
       <c r="AF5" s="5"/>
@@ -918,14 +923,14 @@
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
       <c r="AK5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL5" s="7"/>
       <c r="AM5" s="7"/>
       <c r="AN5" s="7"/>
       <c r="AO5" s="7"/>
       <c r="AP5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ5" s="5"/>
       <c r="AR5" s="5"/>
@@ -936,11 +941,11 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -948,7 +953,7 @@
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -971,7 +976,7 @@
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
@@ -979,7 +984,7 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="7"/>
@@ -1025,15 +1030,15 @@
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
       <c r="AD7" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE7" s="7"/>
       <c r="AF7" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG7" s="7"/>
       <c r="AH7" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7"/>
@@ -1056,7 +1061,7 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1064,7 +1069,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
       <c r="I8" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -1122,7 +1127,7 @@
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
       <c r="I9" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
@@ -1180,7 +1185,7 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
       <c r="I10" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
@@ -1238,7 +1243,7 @@
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
       <c r="I11" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
@@ -1296,7 +1301,7 @@
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
       <c r="I12" s="14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -1358,7 +1363,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
       <c r="I13" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -1416,7 +1421,7 @@
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
       <c r="I14" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
@@ -1474,7 +1479,7 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
@@ -1532,7 +1537,7 @@
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
@@ -1586,7 +1591,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
@@ -1594,7 +1599,7 @@
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
@@ -1652,7 +1657,7 @@
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
       <c r="I18" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
@@ -1710,7 +1715,7 @@
       <c r="G19" s="9"/>
       <c r="H19" s="9"/>
       <c r="I19" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
@@ -1768,7 +1773,7 @@
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14"/>
       <c r="K20" s="14"/>
@@ -1822,7 +1827,7 @@
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
@@ -1830,7 +1835,7 @@
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
       <c r="I21" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J21" s="16"/>
       <c r="K21" s="16"/>
@@ -1974,7 +1979,7 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -2005,7 +2010,7 @@
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AE24" s="18"/>
       <c r="AF24" s="18"/>
